--- a/artfynd/A 43152-2026 artfynd.xlsx
+++ b/artfynd/A 43152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858051</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858030</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857944</v>
       </c>
       <c r="B4" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858084</v>
       </c>
       <c r="B5" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43152-2026 artfynd.xlsx
+++ b/artfynd/A 43152-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136858030</v>
       </c>
       <c r="B3" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858084</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43152-2026 artfynd.xlsx
+++ b/artfynd/A 43152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858051</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858030</v>
       </c>
       <c r="B3" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857944</v>
       </c>
       <c r="B4" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858084</v>
       </c>
       <c r="B5" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43152-2026 artfynd.xlsx
+++ b/artfynd/A 43152-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136858030</v>
       </c>
       <c r="B3" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858084</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43152-2026 artfynd.xlsx
+++ b/artfynd/A 43152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858051</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858030</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857944</v>
       </c>
       <c r="B4" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858084</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43152-2026 artfynd.xlsx
+++ b/artfynd/A 43152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858051</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136858030</v>
       </c>
       <c r="B3" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136857944</v>
       </c>
       <c r="B4" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858084</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
